--- a/template/chip-template.xlsx
+++ b/template/chip-template.xlsx
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:AA2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -453,9 +453,13 @@
     <col min="18" max="18" width="14.83203125" customWidth="1"/>
     <col min="19" max="19" width="16.83203125" customWidth="1"/>
     <col min="20" max="20" width="14.83203125" customWidth="1"/>
-    <col min="21" max="21" width="22.83203125" customWidth="1"/>
-    <col min="22" max="22" width="24.83203125" customWidth="1"/>
-    <col min="23" max="23" width="24.83203125" customWidth="1"/>
+    <col min="21" max="21" width="14.83203125" customWidth="1"/>
+    <col min="22" max="22" width="21.83203125" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" customWidth="1"/>
+    <col min="24" max="24" width="14.83203125" customWidth="1"/>
+    <col min="25" max="25" width="22.83203125" customWidth="1"/>
+    <col min="26" max="26" width="24.83203125" customWidth="1"/>
+    <col min="27" max="27" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,15 +521,27 @@
         <v>currentValue</v>
       </c>
       <c r="T1" t="str">
+        <v>asOfDate</v>
+      </c>
+      <c r="U1" t="str">
+        <v>source</v>
+      </c>
+      <c r="V1" t="str">
+        <v>refreshCycleYears</v>
+      </c>
+      <c r="W1" t="str">
+        <v>direction</v>
+      </c>
+      <c r="X1" t="str">
         <v>dataSource</v>
       </c>
-      <c r="U1" t="str">
+      <c r="Y1" t="str">
         <v>reportingFrequency</v>
       </c>
-      <c r="V1" t="str">
+      <c r="Z1" t="str">
         <v>stateComparisonValue</v>
       </c>
-      <c r="W1" t="str">
+      <c r="AA1" t="str">
         <v>stateComparisonLabel</v>
       </c>
     </row>
@@ -588,28 +604,40 @@
         <v/>
       </c>
       <c r="T2" t="str">
+        <v>(YYYY-MM-DD when currentValue measured, blank if no current)</v>
+      </c>
+      <c r="U2" t="str">
+        <v>(source of currentValue if different from dataSource)</v>
+      </c>
+      <c r="V2" t="str">
+        <v>3  (how many years between measurements)</v>
+      </c>
+      <c r="W2" t="str">
+        <v>higher_is_better  (or lower_is_better)</v>
+      </c>
+      <c r="X2" t="str">
         <v>Orange County Community Health Survey, 2024</v>
       </c>
-      <c r="U2" t="str">
+      <c r="Y2" t="str">
         <v>Every 3 years</v>
       </c>
-      <c r="V2">
+      <c r="Z2">
         <v>51.1</v>
       </c>
-      <c r="W2" t="str">
+      <c r="AA2" t="str">
         <v>NYSDOH Prevention Agenda</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:W2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -619,6 +647,7 @@
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -646,6 +675,9 @@
       <c r="H1" t="str">
         <v>status</v>
       </c>
+      <c r="I1" t="str">
+        <v>lastUpdated</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -672,10 +704,13 @@
       <c r="H2" t="str">
         <v>not_started  (allowed: not_started | in_progress | complete)</v>
       </c>
+      <c r="I2" t="str">
+        <v>(YYYY-MM-DD when status last changed, for activity badge)</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
 </worksheet>
 </file>
